--- a/think3d_repro/outputs/run1/vlmeval_runs/SPAgent_4B_no_tools_general/VSIBench/SPAgent_4B_no_tools_general_VSIBench.xlsx
+++ b/think3d_repro/outputs/run1/vlmeval_runs/SPAgent_4B_no_tools_general/VSIBench/SPAgent_4B_no_tools_general_VSIBench.xlsx
@@ -6012,7 +6012,7 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>8.407493829727173</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -6041,7 +6041,7 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>7.60053014755249</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -6070,7 +6070,7 @@
         <v>1</v>
       </c>
       <c r="I4">
-        <v>5.128363847732544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -6099,7 +6099,7 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>7.809657573699951</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -6128,7 +6128,7 @@
         <v>1</v>
       </c>
       <c r="I6">
-        <v>4.825484752655029</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -6157,7 +6157,7 @@
         <v>1</v>
       </c>
       <c r="I7">
-        <v>5.189071893692017</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -6186,7 +6186,7 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>4.331775426864624</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -6215,7 +6215,7 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>4.26842188835144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -6244,7 +6244,7 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>4.761542081832886</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -6273,7 +6273,7 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>6.67017126083374</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -6302,7 +6302,7 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>4.663599491119385</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -6331,7 +6331,7 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>5.538196086883545</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -6360,7 +6360,7 @@
         <v>0</v>
       </c>
       <c r="I14">
-        <v>4.043775320053101</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -6389,7 +6389,7 @@
         <v>0</v>
       </c>
       <c r="I15">
-        <v>9.627018928527832</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -6418,7 +6418,7 @@
         <v>0</v>
       </c>
       <c r="I16">
-        <v>5.177107334136963</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -6447,7 +6447,7 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <v>4.148416757583618</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -6476,7 +6476,7 @@
         <v>1</v>
       </c>
       <c r="I18">
-        <v>4.765854358673096</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -6505,7 +6505,7 @@
         <v>0</v>
       </c>
       <c r="I19">
-        <v>4.659682273864746</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -6534,7 +6534,7 @@
         <v>1</v>
       </c>
       <c r="I20">
-        <v>3.928623199462891</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -6563,7 +6563,7 @@
         <v>0</v>
       </c>
       <c r="I21">
-        <v>13.47561264038086</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -6592,7 +6592,7 @@
         <v>1</v>
       </c>
       <c r="I22">
-        <v>5.352999210357666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -6621,7 +6621,7 @@
         <v>0</v>
       </c>
       <c r="I23">
-        <v>4.286566257476807</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -6650,7 +6650,7 @@
         <v>0</v>
       </c>
       <c r="I24">
-        <v>11.09629154205322</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -6679,7 +6679,7 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>7.770405292510986</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -6708,7 +6708,7 @@
         <v>0</v>
       </c>
       <c r="I26">
-        <v>4.588910818099976</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -6737,7 +6737,7 @@
         <v>0</v>
       </c>
       <c r="I27">
-        <v>6.409807443618774</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -6766,7 +6766,7 @@
         <v>0</v>
       </c>
       <c r="I28">
-        <v>5.081782102584839</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -6795,7 +6795,7 @@
         <v>0</v>
       </c>
       <c r="I29">
-        <v>3.161885499954224</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -6824,7 +6824,7 @@
         <v>0</v>
       </c>
       <c r="I30">
-        <v>4.324222803115845</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -6853,7 +6853,7 @@
         <v>1</v>
       </c>
       <c r="I31">
-        <v>6.484467267990112</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -6882,7 +6882,7 @@
         <v>0</v>
       </c>
       <c r="I32">
-        <v>8.264254331588745</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -6911,7 +6911,7 @@
         <v>0</v>
       </c>
       <c r="I33">
-        <v>5.016441106796265</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -6940,7 +6940,7 @@
         <v>1</v>
       </c>
       <c r="I34">
-        <v>7.161437511444092</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -6969,7 +6969,7 @@
         <v>0</v>
       </c>
       <c r="I35">
-        <v>16.5437114238739</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -6998,7 +6998,7 @@
         <v>0</v>
       </c>
       <c r="I36">
-        <v>4.299991607666016</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -7027,7 +7027,7 @@
         <v>1</v>
       </c>
       <c r="I37">
-        <v>4.400603055953979</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -7056,7 +7056,7 @@
         <v>0</v>
       </c>
       <c r="I38">
-        <v>2.89398980140686</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -7085,7 +7085,7 @@
         <v>0</v>
       </c>
       <c r="I39">
-        <v>3.237087965011597</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -7114,7 +7114,7 @@
         <v>0</v>
       </c>
       <c r="I40">
-        <v>3.407359600067139</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -7143,7 +7143,7 @@
         <v>1</v>
       </c>
       <c r="I41">
-        <v>7.277721643447876</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -7172,7 +7172,7 @@
         <v>1</v>
       </c>
       <c r="I42">
-        <v>3.967223405838013</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -7201,7 +7201,7 @@
         <v>1</v>
       </c>
       <c r="I43">
-        <v>10.22566771507263</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -7230,7 +7230,7 @@
         <v>0</v>
       </c>
       <c r="I44">
-        <v>6.552587985992432</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -7259,7 +7259,7 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>4.690680742263794</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -7288,7 +7288,7 @@
         <v>0</v>
       </c>
       <c r="I46">
-        <v>3.761759519577026</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -7317,7 +7317,7 @@
         <v>0</v>
       </c>
       <c r="I47">
-        <v>10.81546831130981</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -7346,7 +7346,7 @@
         <v>1</v>
       </c>
       <c r="I48">
-        <v>4.358270168304443</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -7375,7 +7375,7 @@
         <v>0</v>
       </c>
       <c r="I49">
-        <v>5.139167308807373</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -7404,7 +7404,7 @@
         <v>1</v>
       </c>
       <c r="I50">
-        <v>19.61800312995911</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -7433,7 +7433,7 @@
         <v>1</v>
       </c>
       <c r="I51">
-        <v>5.076634883880615</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -7462,7 +7462,7 @@
         <v>1</v>
       </c>
       <c r="I52">
-        <v>12.72088432312012</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -7491,7 +7491,7 @@
         <v>0</v>
       </c>
       <c r="I53">
-        <v>6.523764848709106</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -7520,7 +7520,7 @@
         <v>1</v>
       </c>
       <c r="I54">
-        <v>28.40104007720947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -7549,7 +7549,7 @@
         <v>1</v>
       </c>
       <c r="I55">
-        <v>5.442289113998413</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -7578,7 +7578,7 @@
         <v>1</v>
       </c>
       <c r="I56">
-        <v>6.090767383575439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -7607,7 +7607,7 @@
         <v>0</v>
       </c>
       <c r="I57">
-        <v>3.829801559448242</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -7636,7 +7636,7 @@
         <v>0</v>
       </c>
       <c r="I58">
-        <v>6.976745843887329</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -7665,7 +7665,7 @@
         <v>1</v>
       </c>
       <c r="I59">
-        <v>10.50600075721741</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -7694,7 +7694,7 @@
         <v>1</v>
       </c>
       <c r="I60">
-        <v>11.33786702156067</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -7723,7 +7723,7 @@
         <v>0</v>
       </c>
       <c r="I61">
-        <v>5.494739294052124</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -7752,7 +7752,7 @@
         <v>0</v>
       </c>
       <c r="I62">
-        <v>11.39190363883972</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -7781,7 +7781,7 @@
         <v>1</v>
       </c>
       <c r="I63">
-        <v>7.174252271652222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -7810,7 +7810,7 @@
         <v>1</v>
       </c>
       <c r="I64">
-        <v>10.72759962081909</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -7839,7 +7839,7 @@
         <v>1</v>
       </c>
       <c r="I65">
-        <v>4.630984783172607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -7868,7 +7868,7 @@
         <v>0</v>
       </c>
       <c r="I66">
-        <v>10.57888960838318</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -7897,7 +7897,7 @@
         <v>0</v>
       </c>
       <c r="I67">
-        <v>8.24103569984436</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -7926,7 +7926,7 @@
         <v>1</v>
       </c>
       <c r="I68">
-        <v>5.354566812515259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -7955,7 +7955,7 @@
         <v>1</v>
       </c>
       <c r="I69">
-        <v>3.36273193359375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -7984,7 +7984,7 @@
         <v>0</v>
       </c>
       <c r="I70">
-        <v>6.363786458969116</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -8013,7 +8013,7 @@
         <v>1</v>
       </c>
       <c r="I71">
-        <v>6.43412971496582</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -8042,7 +8042,7 @@
         <v>0</v>
       </c>
       <c r="I72">
-        <v>7.624258041381836</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -8071,7 +8071,7 @@
         <v>0</v>
       </c>
       <c r="I73">
-        <v>7.311596870422363</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -8100,7 +8100,7 @@
         <v>0</v>
       </c>
       <c r="I74">
-        <v>8.922353029251099</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -8129,7 +8129,7 @@
         <v>0</v>
       </c>
       <c r="I75">
-        <v>6.027609586715698</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -8158,7 +8158,7 @@
         <v>0</v>
       </c>
       <c r="I76">
-        <v>28.41076946258545</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -8187,7 +8187,7 @@
         <v>0</v>
       </c>
       <c r="I77">
-        <v>4.455241441726685</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -8216,7 +8216,7 @@
         <v>0</v>
       </c>
       <c r="I78">
-        <v>3.965887308120728</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -8245,7 +8245,7 @@
         <v>1</v>
       </c>
       <c r="I79">
-        <v>5.742569923400879</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -8274,7 +8274,7 @@
         <v>0</v>
       </c>
       <c r="I80">
-        <v>6.356573581695557</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -8303,7 +8303,7 @@
         <v>0</v>
       </c>
       <c r="I81">
-        <v>6.254388570785522</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:9">
@@ -8332,7 +8332,7 @@
         <v>0</v>
       </c>
       <c r="I82">
-        <v>7.399451971054077</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:9">
@@ -8361,7 +8361,7 @@
         <v>1</v>
       </c>
       <c r="I83">
-        <v>4.469957590103149</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -8390,7 +8390,7 @@
         <v>1</v>
       </c>
       <c r="I84">
-        <v>3.929546594619751</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:9">
@@ -8419,7 +8419,7 @@
         <v>0</v>
       </c>
       <c r="I85">
-        <v>4.144909381866455</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:9">
@@ -8448,7 +8448,7 @@
         <v>1</v>
       </c>
       <c r="I86">
-        <v>11.32011198997498</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -8477,7 +8477,7 @@
         <v>0</v>
       </c>
       <c r="I87">
-        <v>5.636337995529175</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:9">
@@ -8506,7 +8506,7 @@
         <v>1</v>
       </c>
       <c r="I88">
-        <v>6.816854953765869</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:9">
@@ -8535,7 +8535,7 @@
         <v>1</v>
       </c>
       <c r="I89">
-        <v>8.072154998779297</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:9">
@@ -8564,7 +8564,7 @@
         <v>0</v>
       </c>
       <c r="I90">
-        <v>6.043214797973633</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:9">
@@ -8593,7 +8593,7 @@
         <v>0</v>
       </c>
       <c r="I91">
-        <v>5.986778259277344</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:9">
@@ -8622,7 +8622,7 @@
         <v>0</v>
       </c>
       <c r="I92">
-        <v>4.30671763420105</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -8651,7 +8651,7 @@
         <v>1</v>
       </c>
       <c r="I93">
-        <v>6.023834228515625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:9">
@@ -8680,7 +8680,7 @@
         <v>0</v>
       </c>
       <c r="I94">
-        <v>6.919973611831665</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:9">
@@ -8709,7 +8709,7 @@
         <v>1</v>
       </c>
       <c r="I95">
-        <v>10.74407720565796</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:9">
@@ -8738,7 +8738,7 @@
         <v>1</v>
       </c>
       <c r="I96">
-        <v>16.79501819610596</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -8767,7 +8767,7 @@
         <v>1</v>
       </c>
       <c r="I97">
-        <v>4.968688249588013</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -8796,7 +8796,7 @@
         <v>1</v>
       </c>
       <c r="I98">
-        <v>6.378272533416748</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:9">
@@ -8825,7 +8825,7 @@
         <v>0</v>
       </c>
       <c r="I99">
-        <v>8.259680986404419</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:9">
@@ -8854,7 +8854,7 @@
         <v>0</v>
       </c>
       <c r="I100">
-        <v>8.96087908744812</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:9">
@@ -8883,7 +8883,7 @@
         <v>0</v>
       </c>
       <c r="I101">
-        <v>5.644945383071899</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:9">
@@ -8912,7 +8912,7 @@
         <v>1</v>
       </c>
       <c r="I102">
-        <v>4.231644630432129</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -8941,7 +8941,7 @@
         <v>0</v>
       </c>
       <c r="I103">
-        <v>5.208795070648193</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:9">
@@ -8970,7 +8970,7 @@
         <v>0</v>
       </c>
       <c r="I104">
-        <v>6.742861032485962</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:9">
@@ -8999,7 +8999,7 @@
         <v>0</v>
       </c>
       <c r="I105">
-        <v>4.853071451187134</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:9">
@@ -9028,7 +9028,7 @@
         <v>1</v>
       </c>
       <c r="I106">
-        <v>5.934623956680298</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -9057,7 +9057,7 @@
         <v>0</v>
       </c>
       <c r="I107">
-        <v>4.952531099319458</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:9">
@@ -9086,7 +9086,7 @@
         <v>0</v>
       </c>
       <c r="I108">
-        <v>10.73174214363098</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -9115,7 +9115,7 @@
         <v>0</v>
       </c>
       <c r="I109">
-        <v>5.341074705123901</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:9">
@@ -9144,7 +9144,7 @@
         <v>0</v>
       </c>
       <c r="I110">
-        <v>7.266602993011475</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:9">
@@ -9173,7 +9173,7 @@
         <v>1</v>
       </c>
       <c r="I111">
-        <v>7.18010425567627</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:9">
@@ -9202,7 +9202,7 @@
         <v>1</v>
       </c>
       <c r="I112">
-        <v>5.416862010955811</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:9">
@@ -9231,7 +9231,7 @@
         <v>1</v>
       </c>
       <c r="I113">
-        <v>7.944979667663574</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:9">
@@ -9260,7 +9260,7 @@
         <v>0</v>
       </c>
       <c r="I114">
-        <v>6.162840843200684</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -9289,7 +9289,7 @@
         <v>1</v>
       </c>
       <c r="I115">
-        <v>6.23525071144104</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -9318,7 +9318,7 @@
         <v>0</v>
       </c>
       <c r="I116">
-        <v>5.325049161911011</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:9">
@@ -9347,7 +9347,7 @@
         <v>1</v>
       </c>
       <c r="I117">
-        <v>5.584362506866455</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:9">
@@ -9376,7 +9376,7 @@
         <v>1</v>
       </c>
       <c r="I118">
-        <v>6.195644378662109</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:9">
@@ -9405,7 +9405,7 @@
         <v>1</v>
       </c>
       <c r="I119">
-        <v>5.983791351318359</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:9">
@@ -9434,7 +9434,7 @@
         <v>0</v>
       </c>
       <c r="I120">
-        <v>6.845393657684326</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:9">
@@ -9463,7 +9463,7 @@
         <v>0</v>
       </c>
       <c r="I121">
-        <v>5.051080465316772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:9">
@@ -9492,7 +9492,7 @@
         <v>0</v>
       </c>
       <c r="I122">
-        <v>4.868134021759033</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:9">
@@ -9521,7 +9521,7 @@
         <v>1</v>
       </c>
       <c r="I123">
-        <v>7.35018253326416</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:9">
@@ -9547,7 +9547,7 @@
         <v>0</v>
       </c>
       <c r="I124">
-        <v>1.666907787322998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:9">
@@ -9576,7 +9576,7 @@
         <v>0</v>
       </c>
       <c r="I125">
-        <v>6.477925777435303</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:9">
@@ -9605,7 +9605,7 @@
         <v>0</v>
       </c>
       <c r="I126">
-        <v>4.183409690856934</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:9">
@@ -9634,7 +9634,7 @@
         <v>1</v>
       </c>
       <c r="I127">
-        <v>12.59631967544556</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:9">
@@ -9663,7 +9663,7 @@
         <v>0</v>
       </c>
       <c r="I128">
-        <v>7.834960460662842</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:9">
@@ -9692,7 +9692,7 @@
         <v>0</v>
       </c>
       <c r="I129">
-        <v>7.79103422164917</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:9">
@@ -9721,7 +9721,7 @@
         <v>0</v>
       </c>
       <c r="I130">
-        <v>4.820624589920044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:9">
@@ -9750,7 +9750,7 @@
         <v>0</v>
       </c>
       <c r="I131">
-        <v>6.664426565170288</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:9">
@@ -9779,7 +9779,7 @@
         <v>1</v>
       </c>
       <c r="I132">
-        <v>5.364714860916138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:9">
@@ -9808,7 +9808,7 @@
         <v>0</v>
       </c>
       <c r="I133">
-        <v>4.45445990562439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:9">
@@ -9837,7 +9837,7 @@
         <v>0</v>
       </c>
       <c r="I134">
-        <v>4.797508955001831</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135" spans="1:9">
@@ -9866,7 +9866,7 @@
         <v>0</v>
       </c>
       <c r="I135">
-        <v>5.359574794769287</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:9">
@@ -9895,7 +9895,7 @@
         <v>1</v>
       </c>
       <c r="I136">
-        <v>21.80970072746277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137" spans="1:9">
@@ -9924,7 +9924,7 @@
         <v>1</v>
       </c>
       <c r="I137">
-        <v>5.437515735626221</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:9">
@@ -9953,7 +9953,7 @@
         <v>0</v>
       </c>
       <c r="I138">
-        <v>5.859800815582275</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:9">
@@ -9982,7 +9982,7 @@
         <v>0</v>
       </c>
       <c r="I139">
-        <v>13.86056113243103</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:9">
@@ -10011,7 +10011,7 @@
         <v>1</v>
       </c>
       <c r="I140">
-        <v>5.021439075469971</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:9">
@@ -10040,7 +10040,7 @@
         <v>1</v>
       </c>
       <c r="I141">
-        <v>5.223702907562256</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:9">
@@ -10069,7 +10069,7 @@
         <v>0</v>
       </c>
       <c r="I142">
-        <v>4.880969285964966</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:9">
@@ -10098,7 +10098,7 @@
         <v>1</v>
       </c>
       <c r="I143">
-        <v>4.711888313293457</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:9">
@@ -10127,7 +10127,7 @@
         <v>1</v>
       </c>
       <c r="I144">
-        <v>6.530718564987183</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:9">
@@ -10156,7 +10156,7 @@
         <v>1</v>
       </c>
       <c r="I145">
-        <v>5.279051065444946</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:9">
@@ -10185,7 +10185,7 @@
         <v>0</v>
       </c>
       <c r="I146">
-        <v>3.668230772018433</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147" spans="1:9">
@@ -10214,7 +10214,7 @@
         <v>1</v>
       </c>
       <c r="I147">
-        <v>3.318042039871216</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148" spans="1:9">
@@ -10243,7 +10243,7 @@
         <v>0</v>
       </c>
       <c r="I148">
-        <v>38.05913090705872</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:9">
@@ -10272,7 +10272,7 @@
         <v>0</v>
       </c>
       <c r="I149">
-        <v>5.260888814926147</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:9">
@@ -10301,7 +10301,7 @@
         <v>0</v>
       </c>
       <c r="I150">
-        <v>5.314348220825195</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151" spans="1:9">
@@ -10330,7 +10330,7 @@
         <v>1</v>
       </c>
       <c r="I151">
-        <v>8.757960081100464</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:9">
@@ -10359,7 +10359,7 @@
         <v>0</v>
       </c>
       <c r="I152">
-        <v>10.2186017036438</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153" spans="1:9">
@@ -10388,7 +10388,7 @@
         <v>1</v>
       </c>
       <c r="I153">
-        <v>6.320015668869019</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154" spans="1:9">
@@ -10417,7 +10417,7 @@
         <v>1</v>
       </c>
       <c r="I154">
-        <v>31.48726892471313</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155" spans="1:9">
@@ -10446,7 +10446,7 @@
         <v>0</v>
       </c>
       <c r="I155">
-        <v>34.04001045227051</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156" spans="1:9">
@@ -10475,7 +10475,7 @@
         <v>0</v>
       </c>
       <c r="I156">
-        <v>28.33262228965759</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157" spans="1:9">
@@ -10501,7 +10501,7 @@
         <v>0</v>
       </c>
       <c r="I157">
-        <v>34.42253923416138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158" spans="1:9">
@@ -10530,7 +10530,7 @@
         <v>0</v>
       </c>
       <c r="I158">
-        <v>36.34724426269531</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159" spans="1:9">
@@ -10559,7 +10559,7 @@
         <v>0</v>
       </c>
       <c r="I159">
-        <v>28.44647312164307</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160" spans="1:9">
@@ -10588,7 +10588,7 @@
         <v>1</v>
       </c>
       <c r="I160">
-        <v>33.4751250743866</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161" spans="1:9">
@@ -10617,7 +10617,7 @@
         <v>1</v>
       </c>
       <c r="I161">
-        <v>23.27708625793457</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162" spans="1:9">
@@ -10646,7 +10646,7 @@
         <v>0</v>
       </c>
       <c r="I162">
-        <v>5.844784498214722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163" spans="1:9">
@@ -10675,7 +10675,7 @@
         <v>1</v>
       </c>
       <c r="I163">
-        <v>27.55791735649109</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164" spans="1:9">
@@ -10704,7 +10704,7 @@
         <v>1</v>
       </c>
       <c r="I164">
-        <v>6.399728298187256</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165" spans="1:9">
@@ -10733,7 +10733,7 @@
         <v>0</v>
       </c>
       <c r="I165">
-        <v>32.25017189979553</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166" spans="1:9">
@@ -10762,7 +10762,7 @@
         <v>0</v>
       </c>
       <c r="I166">
-        <v>6.853149890899658</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167" spans="1:9">
@@ -10791,7 +10791,7 @@
         <v>0</v>
       </c>
       <c r="I167">
-        <v>12.63951826095581</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168" spans="1:9">
@@ -10820,7 +10820,7 @@
         <v>1</v>
       </c>
       <c r="I168">
-        <v>10.40158438682556</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169" spans="1:9">
@@ -10849,7 +10849,7 @@
         <v>0</v>
       </c>
       <c r="I169">
-        <v>29.54359865188599</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170" spans="1:9">
@@ -10878,7 +10878,7 @@
         <v>1</v>
       </c>
       <c r="I170">
-        <v>10.492671251297</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171" spans="1:9">
@@ -10907,7 +10907,7 @@
         <v>0</v>
       </c>
       <c r="I171">
-        <v>20.69471740722656</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172" spans="1:9">
@@ -10936,7 +10936,7 @@
         <v>1</v>
       </c>
       <c r="I172">
-        <v>7.506313562393188</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173" spans="1:9">
@@ -10965,7 +10965,7 @@
         <v>1</v>
       </c>
       <c r="I173">
-        <v>34.83458232879639</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174" spans="1:9">
@@ -10994,7 +10994,7 @@
         <v>0</v>
       </c>
       <c r="I174">
-        <v>10.01018571853638</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175" spans="1:9">
@@ -11023,7 +11023,7 @@
         <v>1</v>
       </c>
       <c r="I175">
-        <v>17.32035279273987</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176" spans="1:9">
@@ -11052,7 +11052,7 @@
         <v>0</v>
       </c>
       <c r="I176">
-        <v>5.615953683853149</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177" spans="1:9">
@@ -11081,7 +11081,7 @@
         <v>1</v>
       </c>
       <c r="I177">
-        <v>11.78951525688171</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178" spans="1:9">
@@ -11110,7 +11110,7 @@
         <v>0</v>
       </c>
       <c r="I178">
-        <v>7.802807092666626</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179" spans="1:9">
@@ -11139,7 +11139,7 @@
         <v>0</v>
       </c>
       <c r="I179">
-        <v>8.148082733154297</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180" spans="1:9">
@@ -11168,7 +11168,7 @@
         <v>0</v>
       </c>
       <c r="I180">
-        <v>26.07448244094849</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181" spans="1:9">
@@ -11197,7 +11197,7 @@
         <v>0</v>
       </c>
       <c r="I181">
-        <v>7.064181804656982</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182" spans="1:9">
@@ -11226,7 +11226,7 @@
         <v>0</v>
       </c>
       <c r="I182">
-        <v>25.33912968635559</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183" spans="1:9">
@@ -11252,7 +11252,7 @@
         <v>0</v>
       </c>
       <c r="I183">
-        <v>27.88970637321472</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184" spans="1:9">
@@ -11281,7 +11281,7 @@
         <v>0</v>
       </c>
       <c r="I184">
-        <v>16.1691529750824</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185" spans="1:9">
@@ -11310,7 +11310,7 @@
         <v>0</v>
       </c>
       <c r="I185">
-        <v>32.52516674995422</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186" spans="1:9">
@@ -11339,7 +11339,7 @@
         <v>1</v>
       </c>
       <c r="I186">
-        <v>7.079241991043091</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187" spans="1:9">
@@ -11365,7 +11365,7 @@
         <v>0</v>
       </c>
       <c r="I187">
-        <v>24.39953637123108</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188" spans="1:9">
@@ -11394,7 +11394,7 @@
         <v>0</v>
       </c>
       <c r="I188">
-        <v>33.48284435272217</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189" spans="1:9">
@@ -11423,7 +11423,7 @@
         <v>0</v>
       </c>
       <c r="I189">
-        <v>28.04616236686707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190" spans="1:9">
@@ -11452,7 +11452,7 @@
         <v>0</v>
       </c>
       <c r="I190">
-        <v>14.83737850189209</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191" spans="1:9">
@@ -11481,7 +11481,7 @@
         <v>0</v>
       </c>
       <c r="I191">
-        <v>27.80967950820923</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192" spans="1:9">
@@ -11510,7 +11510,7 @@
         <v>1</v>
       </c>
       <c r="I192">
-        <v>4.785346269607544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193" spans="1:9">
@@ -11539,7 +11539,7 @@
         <v>0</v>
       </c>
       <c r="I193">
-        <v>36.18127131462097</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194" spans="1:9">
@@ -11568,7 +11568,7 @@
         <v>1</v>
       </c>
       <c r="I194">
-        <v>26.97446084022522</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195" spans="1:9">
@@ -11597,7 +11597,7 @@
         <v>0</v>
       </c>
       <c r="I195">
-        <v>25.61878967285156</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196" spans="1:9">
@@ -11626,7 +11626,7 @@
         <v>0</v>
       </c>
       <c r="I196">
-        <v>11.62862658500671</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197" spans="1:9">
@@ -11655,7 +11655,7 @@
         <v>0</v>
       </c>
       <c r="I197">
-        <v>31.52055668830872</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198" spans="1:9">
@@ -11684,7 +11684,7 @@
         <v>1</v>
       </c>
       <c r="I198">
-        <v>8.437889099121094</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199" spans="1:9">
@@ -11713,7 +11713,7 @@
         <v>1</v>
       </c>
       <c r="I199">
-        <v>5.048314332962036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200" spans="1:9">
@@ -11742,7 +11742,7 @@
         <v>0</v>
       </c>
       <c r="I200">
-        <v>36.22856307029724</v>
+        <v>0</v>
       </c>
     </row>
     <row r="201" spans="1:9">
@@ -11771,7 +11771,7 @@
         <v>1</v>
       </c>
       <c r="I201">
-        <v>7.339195728302002</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
